--- a/output/yearly_benthic_cover_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_50_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.62675563460478</v>
+        <v>45.19659523891223</v>
       </c>
       <c r="M2" t="n">
-        <v>99.88733886154816</v>
+        <v>100.6023031768418</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.11052634399363</v>
+        <v>88.12532128189662</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95883349987001</v>
+        <v>45.96820523618398</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228921057256059</v>
+        <v>2.228951841278988</v>
       </c>
       <c r="E3" t="n">
-        <v>5.728148775627528</v>
+        <v>5.73430121923437</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429736857520198</v>
+        <v>0.7429839470929962</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98271137919167</v>
+        <v>33.98581120134477</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17678954459291</v>
+        <v>34.17726156627782</v>
       </c>
       <c r="I3" t="n">
-        <v>6.607396365623318</v>
+        <v>6.612361837336452</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643585535950124</v>
+        <v>4.643649669331226</v>
       </c>
       <c r="K3" t="n">
-        <v>11.88947365600637</v>
+        <v>11.87467871810337</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91454146205511</v>
+        <v>48.9197897216574</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7628486179315</v>
+        <v>106.7626736759448</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.30612605078286</v>
+        <v>87.28022116040492</v>
       </c>
       <c r="C4" t="n">
-        <v>42.79604854428641</v>
+        <v>42.76533167597836</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190776147937706</v>
+        <v>2.188653590238014</v>
       </c>
       <c r="E4" t="n">
-        <v>6.549746631312274</v>
+        <v>6.550948491035477</v>
       </c>
       <c r="F4" t="n">
-        <v>0.74453888823319</v>
+        <v>0.7445508158313815</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40114414973275</v>
+        <v>33.37136600506047</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24878885872673</v>
+        <v>34.24933752824354</v>
       </c>
       <c r="I4" t="n">
-        <v>5.517763323382762</v>
+        <v>5.521922131049899</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653368051457438</v>
+        <v>4.653442598946134</v>
       </c>
       <c r="K4" t="n">
-        <v>12.69387394921715</v>
+        <v>12.71977883959509</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32653871856246</v>
+        <v>44.33121276672276</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81646121206602</v>
+        <v>99.81632328229621</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.21178498729783</v>
+        <v>86.25566331674408</v>
       </c>
       <c r="C5" t="n">
-        <v>42.55822077086741</v>
+        <v>42.59789468781699</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137686222742501</v>
+        <v>2.139207863529036</v>
       </c>
       <c r="E5" t="n">
-        <v>7.158744995539946</v>
+        <v>7.171250347701549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458649205614325</v>
+        <v>0.7458771943709556</v>
       </c>
       <c r="G5" t="n">
-        <v>32.59172131298477</v>
+        <v>32.61744521524189</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30978634582588</v>
+        <v>34.31035094106395</v>
       </c>
       <c r="I5" t="n">
-        <v>4.606325436134338</v>
+        <v>4.609799290018221</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661655753508953</v>
+        <v>4.661732464818472</v>
       </c>
       <c r="K5" t="n">
-        <v>13.78821501270216</v>
+        <v>13.74433668325593</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50029301300314</v>
+        <v>43.5043819030646</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84672879657272</v>
+        <v>99.84661327413751</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.87345825610336</v>
+        <v>84.93865691943647</v>
       </c>
       <c r="C6" t="n">
-        <v>41.9354581423195</v>
+        <v>41.99702412492723</v>
       </c>
       <c r="D6" t="n">
-        <v>2.072511610751586</v>
+        <v>2.075141141301327</v>
       </c>
       <c r="E6" t="n">
-        <v>7.581219761926765</v>
+        <v>7.597696531926669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469910689711641</v>
+        <v>0.7470033454913897</v>
       </c>
       <c r="G6" t="n">
-        <v>31.59805219162761</v>
+        <v>31.64059166210701</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36158917267354</v>
+        <v>34.36215389260392</v>
       </c>
       <c r="I6" t="n">
-        <v>3.844400269082914</v>
+        <v>3.847299436684961</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668694181069776</v>
+        <v>4.668770909321186</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12654174389664</v>
+        <v>15.06134308056354</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81004662944679</v>
+        <v>42.81358281423094</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87204651566293</v>
+        <v>99.87195001972171</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.32431871449248</v>
+        <v>83.39820159745435</v>
       </c>
       <c r="C7" t="n">
-        <v>40.98357957348333</v>
+        <v>41.05432450282831</v>
       </c>
       <c r="D7" t="n">
-        <v>1.997241689564359</v>
+        <v>2.00032857145422</v>
       </c>
       <c r="E7" t="n">
-        <v>7.840513062690184</v>
+        <v>7.858818663127436</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479496452714112</v>
+        <v>0.7479618104212135</v>
       </c>
       <c r="G7" t="n">
-        <v>30.450467355048</v>
+        <v>30.49989143376458</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40568368248491</v>
+        <v>34.40624327937581</v>
       </c>
       <c r="I7" t="n">
-        <v>3.207777996487311</v>
+        <v>3.210196524178493</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67468528294632</v>
+        <v>4.674761315132584</v>
       </c>
       <c r="K7" t="n">
-        <v>16.67568128550751</v>
+        <v>16.60179840254566</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23395024464574</v>
+        <v>42.23700766582924</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89321110363657</v>
+        <v>99.8931305712032</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.08358348834338</v>
+        <v>88.17031820479622</v>
       </c>
       <c r="C8" t="n">
-        <v>43.22214866838343</v>
+        <v>43.35517254642269</v>
       </c>
       <c r="D8" t="n">
-        <v>2.001479117363124</v>
+        <v>2.004533878116865</v>
       </c>
       <c r="E8" t="n">
-        <v>9.629027075544542</v>
+        <v>9.686207867051088</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495365251345294</v>
+        <v>0.7495342564831531</v>
       </c>
       <c r="G8" t="n">
-        <v>30.93380778855478</v>
+        <v>31.00604246878198</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47868015618834</v>
+        <v>34.47857579822504</v>
       </c>
       <c r="I8" t="n">
-        <v>5.606449543467268</v>
+        <v>5.560834833118391</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684603282090809</v>
+        <v>4.684589103019706</v>
       </c>
       <c r="K8" t="n">
-        <v>11.9164165116566</v>
+        <v>11.82968179520379</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6749488246526</v>
+        <v>44.63017336599078</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81351400469262</v>
+        <v>99.81502770761725</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.13266433222232</v>
+        <v>86.05797134558402</v>
       </c>
       <c r="C9" t="n">
-        <v>42.1416048981797</v>
+        <v>42.10630978248734</v>
       </c>
       <c r="D9" t="n">
-        <v>1.91320130278088</v>
+        <v>1.908789292182185</v>
       </c>
       <c r="E9" t="n">
-        <v>9.984410434840131</v>
+        <v>9.997282643974655</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508942015896468</v>
+        <v>0.7508820336795269</v>
       </c>
       <c r="G9" t="n">
-        <v>29.56943235011479</v>
+        <v>29.52506939566259</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54113327312374</v>
+        <v>34.54057354925823</v>
       </c>
       <c r="I9" t="n">
-        <v>4.680504009837831</v>
+        <v>4.642361720329792</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693088759935293</v>
+        <v>4.693012710497043</v>
       </c>
       <c r="K9" t="n">
-        <v>13.86733566777766</v>
+        <v>13.94202865441597</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83532472450187</v>
+        <v>43.7971939288434</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84426529045925</v>
+        <v>99.84553236574672</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.0966432744536</v>
+        <v>83.74747067259331</v>
       </c>
       <c r="C10" t="n">
-        <v>40.83198723292308</v>
+        <v>40.51629515366514</v>
       </c>
       <c r="D10" t="n">
-        <v>1.822080566758031</v>
+        <v>1.805120897244643</v>
       </c>
       <c r="E10" t="n">
-        <v>10.15995584893865</v>
+        <v>10.10008630862491</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520568868108423</v>
+        <v>0.7520400261410285</v>
       </c>
       <c r="G10" t="n">
-        <v>28.16111821421913</v>
+        <v>27.9215311909985</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59461679329873</v>
+        <v>34.59384120248731</v>
       </c>
       <c r="I10" t="n">
-        <v>3.906459421860445</v>
+        <v>3.874600883715481</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700355542567764</v>
+        <v>4.700250163381428</v>
       </c>
       <c r="K10" t="n">
-        <v>15.9033567255464</v>
+        <v>16.25252932740671</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13464204125722</v>
+        <v>43.10222102669677</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86998599972671</v>
+        <v>99.87104550776861</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.82858167636704</v>
+        <v>81.29472442830031</v>
       </c>
       <c r="C11" t="n">
-        <v>39.16971372723183</v>
+        <v>38.66417119034324</v>
       </c>
       <c r="D11" t="n">
-        <v>1.721416992386323</v>
+        <v>1.696197407776926</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14193810327802</v>
+        <v>10.02948555298849</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530555126177096</v>
+        <v>0.7530369877105153</v>
       </c>
       <c r="G11" t="n">
-        <v>26.60531499153762</v>
+        <v>26.2367074136839</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64055358041463</v>
+        <v>34.63970143468371</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25970554227205</v>
+        <v>3.233114458266052</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706596953860685</v>
+        <v>4.706481173190721</v>
       </c>
       <c r="K11" t="n">
-        <v>18.17141832363296</v>
+        <v>18.70527557169969</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55035518741687</v>
+        <v>42.52292543563164</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89148723828166</v>
+        <v>99.89237219767458</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.54657861849117</v>
+        <v>78.82577464159917</v>
       </c>
       <c r="C12" t="n">
-        <v>37.39245942281492</v>
+        <v>36.69552125021787</v>
       </c>
       <c r="D12" t="n">
-        <v>1.621146017610644</v>
+        <v>1.587691180056606</v>
       </c>
       <c r="E12" t="n">
-        <v>10.00443224506696</v>
+        <v>9.837452394840151</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539136878841426</v>
+        <v>0.7538959255346653</v>
       </c>
       <c r="G12" t="n">
-        <v>25.05557958157325</v>
+        <v>24.55833782285205</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68002964267055</v>
+        <v>34.67921257459461</v>
       </c>
       <c r="I12" t="n">
-        <v>2.719516894409741</v>
+        <v>2.697335209129415</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711960549275891</v>
+        <v>4.711849534591658</v>
       </c>
       <c r="K12" t="n">
-        <v>20.45342138150884</v>
+        <v>21.17422535840083</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06357181950202</v>
+        <v>42.04044465642947</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90945262382577</v>
+        <v>99.91019126504818</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.16138905124868</v>
+        <v>76.36085104449238</v>
       </c>
       <c r="C13" t="n">
-        <v>35.42759264467163</v>
+        <v>34.64708361633355</v>
       </c>
       <c r="D13" t="n">
-        <v>1.517216495384888</v>
+        <v>1.480384469139925</v>
       </c>
       <c r="E13" t="n">
-        <v>9.741142182013807</v>
+        <v>9.547569890904446</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546525037963772</v>
+        <v>0.7546363817787936</v>
       </c>
       <c r="G13" t="n">
-        <v>23.4492995878437</v>
+        <v>22.89852230554406</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71401517463334</v>
+        <v>34.71327356182451</v>
       </c>
       <c r="I13" t="n">
-        <v>2.268484958849211</v>
+        <v>2.249987049183192</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716578148727357</v>
+        <v>4.716477386117459</v>
       </c>
       <c r="K13" t="n">
-        <v>22.83861094875133</v>
+        <v>23.63914895550761</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65825427062123</v>
+        <v>41.63884145012744</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9244578640442</v>
+        <v>99.92507402196861</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.76651700344478</v>
+        <v>83.41419720482169</v>
       </c>
       <c r="C14" t="n">
-        <v>39.48234568227405</v>
+        <v>38.99200318368224</v>
       </c>
       <c r="D14" t="n">
-        <v>1.519025802587734</v>
+        <v>1.482153222584335</v>
       </c>
       <c r="E14" t="n">
-        <v>12.01490569295018</v>
+        <v>11.9661544526775</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555524401040286</v>
+        <v>0.7555380162713011</v>
       </c>
       <c r="G14" t="n">
-        <v>25.23994513429992</v>
+        <v>24.83474487628702</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51809409141686</v>
+        <v>36.66361231820372</v>
       </c>
       <c r="I14" t="n">
-        <v>2.996791091435885</v>
+        <v>2.989881717102203</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722202750650179</v>
+        <v>4.722112601695631</v>
       </c>
       <c r="K14" t="n">
-        <v>16.23348299655524</v>
+        <v>16.58580279517829</v>
       </c>
       <c r="L14" t="n">
-        <v>44.18439726709379</v>
+        <v>44.32265023148893</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90022594592307</v>
+        <v>99.90045621034946</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.10080370267202</v>
+        <v>82.63943136906124</v>
       </c>
       <c r="C15" t="n">
-        <v>39.27993675409078</v>
+        <v>38.67908608165722</v>
       </c>
       <c r="D15" t="n">
-        <v>1.494442489065859</v>
+        <v>1.453618540809138</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23709954770218</v>
+        <v>12.15145898928565</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563100551981181</v>
+        <v>0.7562980925724487</v>
       </c>
       <c r="G15" t="n">
-        <v>24.83147183288896</v>
+        <v>24.35662187846535</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55471187970331</v>
+        <v>36.70049615758358</v>
       </c>
       <c r="I15" t="n">
-        <v>2.499830053125365</v>
+        <v>2.494074631767282</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726937844988239</v>
+        <v>4.726863078577804</v>
       </c>
       <c r="K15" t="n">
-        <v>16.89919629732796</v>
+        <v>17.36056863093875</v>
       </c>
       <c r="L15" t="n">
-        <v>43.73762275159694</v>
+        <v>43.87729301748452</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91675580301569</v>
+        <v>99.91694773008049</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.75875619689791</v>
+        <v>80.21423965021442</v>
       </c>
       <c r="C16" t="n">
-        <v>37.32447503757059</v>
+        <v>36.63920503669789</v>
       </c>
       <c r="D16" t="n">
-        <v>1.404888495301222</v>
+        <v>1.361930071687704</v>
       </c>
       <c r="E16" t="n">
-        <v>11.85129263660557</v>
+        <v>11.73169203732482</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569609215526545</v>
+        <v>0.7569518606847201</v>
       </c>
       <c r="G16" t="n">
-        <v>23.34345373252077</v>
+        <v>22.82030316051406</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58617018426867</v>
+        <v>36.73222123309019</v>
       </c>
       <c r="I16" t="n">
-        <v>2.08498446694492</v>
+        <v>2.080192157633438</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731005759704091</v>
+        <v>4.7309491292795</v>
       </c>
       <c r="K16" t="n">
-        <v>19.24124380310211</v>
+        <v>19.78576034978556</v>
       </c>
       <c r="L16" t="n">
-        <v>43.36484143562934</v>
+        <v>43.50575476263411</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93056027630205</v>
+        <v>99.93072014911758</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.45855417203082</v>
+        <v>82.02229494469466</v>
       </c>
       <c r="C17" t="n">
-        <v>38.55910715190856</v>
+        <v>37.94717946163732</v>
       </c>
       <c r="D17" t="n">
-        <v>1.406073760077255</v>
+        <v>1.363080995832203</v>
       </c>
       <c r="E17" t="n">
-        <v>12.63697407087909</v>
+        <v>12.55358270296215</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575995481199231</v>
+        <v>0.7575915368258058</v>
       </c>
       <c r="G17" t="n">
-        <v>23.79099100335719</v>
+        <v>23.30499219042001</v>
       </c>
       <c r="H17" t="n">
-        <v>37.04487996125182</v>
+        <v>37.22866678613846</v>
       </c>
       <c r="I17" t="n">
-        <v>2.08703865259601</v>
+        <v>2.079433627354744</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734997175749521</v>
+        <v>4.734947105161286</v>
       </c>
       <c r="K17" t="n">
-        <v>17.54144582796918</v>
+        <v>17.97770505530534</v>
       </c>
       <c r="L17" t="n">
-        <v>43.82993770808068</v>
+        <v>44.00585955481262</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93049068795843</v>
+        <v>99.93074407175527</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.16062640808552</v>
+        <v>79.61336096783019</v>
       </c>
       <c r="C18" t="n">
-        <v>36.58357709801538</v>
+        <v>35.85912367519718</v>
       </c>
       <c r="D18" t="n">
-        <v>1.321628813778974</v>
+        <v>1.275789909596551</v>
       </c>
       <c r="E18" t="n">
-        <v>12.16810822018754</v>
+        <v>12.03867690271397</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581478513417838</v>
+        <v>0.7581415928518951</v>
       </c>
       <c r="G18" t="n">
-        <v>22.36216912024987</v>
+        <v>21.81255110347407</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0716907309871</v>
+        <v>37.25569698844878</v>
       </c>
       <c r="I18" t="n">
-        <v>1.740457600654098</v>
+        <v>1.734119515420581</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73842407088615</v>
+        <v>4.738384955324344</v>
       </c>
       <c r="K18" t="n">
-        <v>19.83937359191448</v>
+        <v>20.38663903216982</v>
       </c>
       <c r="L18" t="n">
-        <v>43.51907601416468</v>
+        <v>43.69647524742869</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94202670409454</v>
+        <v>99.9422379547957</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.25350134683852</v>
+        <v>78.68404840846719</v>
       </c>
       <c r="C19" t="n">
-        <v>35.94465916662423</v>
+        <v>35.19669688197079</v>
       </c>
       <c r="D19" t="n">
-        <v>1.288975254491903</v>
+        <v>1.242798731262321</v>
       </c>
       <c r="E19" t="n">
-        <v>12.10934784101627</v>
+        <v>11.96836125335681</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586106173017807</v>
+        <v>0.7586060077100434</v>
       </c>
       <c r="G19" t="n">
-        <v>21.809665718733</v>
+        <v>21.24849133315751</v>
       </c>
       <c r="H19" t="n">
-        <v>37.09431892484068</v>
+        <v>37.27851871382994</v>
       </c>
       <c r="I19" t="n">
-        <v>1.451266632318747</v>
+        <v>1.445984820962803</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741316358136131</v>
+        <v>4.741287548187771</v>
       </c>
       <c r="K19" t="n">
-        <v>20.74649865316149</v>
+        <v>21.31595159153281</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26049613575166</v>
+        <v>43.43918153995693</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95165395553738</v>
+        <v>99.95183001346054</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.77713112016932</v>
+        <v>76.15271994531426</v>
       </c>
       <c r="C20" t="n">
-        <v>33.69179401491803</v>
+        <v>32.88776008746748</v>
       </c>
       <c r="D20" t="n">
-        <v>1.198944105233435</v>
+        <v>1.152113206782741</v>
       </c>
       <c r="E20" t="n">
-        <v>11.46521603330715</v>
+        <v>11.29598157587638</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590091462182621</v>
+        <v>0.759006340550069</v>
       </c>
       <c r="G20" t="n">
-        <v>20.28632439564875</v>
+        <v>19.6980145484009</v>
       </c>
       <c r="H20" t="n">
-        <v>37.11380607462684</v>
+        <v>37.29819139650972</v>
       </c>
       <c r="I20" t="n">
-        <v>1.210024201270736</v>
+        <v>1.205623248756529</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743807163864139</v>
+        <v>4.743789628437931</v>
       </c>
       <c r="K20" t="n">
-        <v>23.22286887983069</v>
+        <v>23.84728005468574</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04502414324243</v>
+        <v>43.22479361282004</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95968703799115</v>
+        <v>99.95983375497326</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.34386640522071</v>
+        <v>82.07681139471148</v>
       </c>
       <c r="C21" t="n">
-        <v>37.09424404147691</v>
+        <v>36.54811438811497</v>
       </c>
       <c r="D21" t="n">
-        <v>1.199813051382289</v>
+        <v>1.152933954779072</v>
       </c>
       <c r="E21" t="n">
-        <v>13.31632605508183</v>
+        <v>13.2730013216934</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595592453193566</v>
+        <v>0.7595470451696681</v>
       </c>
       <c r="G21" t="n">
-        <v>21.84543009603382</v>
+        <v>21.38866838953302</v>
       </c>
       <c r="H21" t="n">
-        <v>38.68510765248111</v>
+        <v>39.00138333702139</v>
       </c>
       <c r="I21" t="n">
-        <v>1.790385021676327</v>
+        <v>1.754108314204511</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74724528324598</v>
+        <v>4.747169032310425</v>
       </c>
       <c r="K21" t="n">
-        <v>17.65613359477929</v>
+        <v>17.92318860528851</v>
       </c>
       <c r="L21" t="n">
-        <v>45.18998608498175</v>
+        <v>45.47026835314402</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94036372123796</v>
+        <v>99.94157134654751</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_50_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.19659523891223</v>
+        <v>45.28058381978849</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6023031768418</v>
+        <v>100.1242315168494</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.12532128189662</v>
+        <v>87.97412231796558</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96820523618398</v>
+        <v>45.90425514520628</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228951841278988</v>
+        <v>2.228612641612747</v>
       </c>
       <c r="E3" t="n">
-        <v>5.73430121923437</v>
+        <v>5.689483872280083</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429839470929962</v>
+        <v>0.7428708805375824</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98581120134477</v>
+        <v>33.96520065574613</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17726156627782</v>
+        <v>34.17206050472879</v>
       </c>
       <c r="I3" t="n">
-        <v>6.612361837336452</v>
+        <v>6.532950759700363</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643649669331226</v>
+        <v>4.64294300335989</v>
       </c>
       <c r="K3" t="n">
-        <v>11.87467871810337</v>
+        <v>12.02587768203442</v>
       </c>
       <c r="L3" t="n">
-        <v>48.9197897216574</v>
+        <v>48.83535532847674</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7626736759448</v>
+        <v>106.7654881557174</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.28022116040492</v>
+        <v>87.0282930925122</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76533167597836</v>
+        <v>42.58769309690378</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188653590238014</v>
+        <v>2.182836651729841</v>
       </c>
       <c r="E4" t="n">
-        <v>6.550948491035477</v>
+        <v>6.481871377939024</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445508158313815</v>
+        <v>0.7444231470448968</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37136600506047</v>
+        <v>33.26755107207368</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24933752824354</v>
+        <v>34.24346476406525</v>
       </c>
       <c r="I4" t="n">
-        <v>5.521922131049899</v>
+        <v>5.455501410628896</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653442598946134</v>
+        <v>4.652644669030605</v>
       </c>
       <c r="K4" t="n">
-        <v>12.71977883959509</v>
+        <v>12.97170690748779</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33121276672276</v>
+        <v>44.25912914117232</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81632328229621</v>
+        <v>99.8185291455639</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.25566331674408</v>
+        <v>85.73149626915436</v>
       </c>
       <c r="C5" t="n">
-        <v>42.59789468781699</v>
+        <v>42.13759395468361</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139207863529036</v>
+        <v>2.119076002777747</v>
       </c>
       <c r="E5" t="n">
-        <v>7.171250347701549</v>
+        <v>7.051586194127362</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458771943709556</v>
+        <v>0.7457413430424721</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61744521524189</v>
+        <v>32.29580605225215</v>
       </c>
       <c r="H5" t="n">
-        <v>34.31035094106395</v>
+        <v>34.30410177995371</v>
       </c>
       <c r="I5" t="n">
-        <v>4.609799290018221</v>
+        <v>4.554301502985467</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661732464818472</v>
+        <v>4.660883394015451</v>
       </c>
       <c r="K5" t="n">
-        <v>13.74433668325593</v>
+        <v>14.26850373084564</v>
       </c>
       <c r="L5" t="n">
-        <v>43.5043819030646</v>
+        <v>43.44236060861994</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84661327413751</v>
+        <v>99.84845829414918</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.93865691943647</v>
+        <v>84.28814907434025</v>
       </c>
       <c r="C6" t="n">
-        <v>41.99702412492723</v>
+        <v>41.40140427280026</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075141141301327</v>
+        <v>2.048390542792962</v>
       </c>
       <c r="E6" t="n">
-        <v>7.597696531926669</v>
+        <v>7.449860977871965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7470033454913897</v>
+        <v>0.7468623112740397</v>
       </c>
       <c r="G6" t="n">
-        <v>31.64059166210701</v>
+        <v>31.21852335762939</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36215389260392</v>
+        <v>34.35566631860582</v>
       </c>
       <c r="I6" t="n">
-        <v>3.847299436684961</v>
+        <v>3.80095612070332</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668770909321186</v>
+        <v>4.667889445462748</v>
       </c>
       <c r="K6" t="n">
-        <v>15.06134308056354</v>
+        <v>15.71185092565976</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81358281423094</v>
+        <v>42.76023642645705</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87195001972171</v>
+        <v>99.87349162491707</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.39820159745435</v>
+        <v>82.66998497707348</v>
       </c>
       <c r="C7" t="n">
-        <v>41.05432450282831</v>
+        <v>40.37338366462151</v>
       </c>
       <c r="D7" t="n">
-        <v>2.00032857145422</v>
+        <v>1.969498853817399</v>
       </c>
       <c r="E7" t="n">
-        <v>7.858818663127436</v>
+        <v>7.691522777279719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479618104212135</v>
+        <v>0.7478173875454563</v>
       </c>
       <c r="G7" t="n">
-        <v>30.49989143376458</v>
+        <v>30.01617352074315</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40624327937581</v>
+        <v>34.39959982709099</v>
       </c>
       <c r="I7" t="n">
-        <v>3.210196524178493</v>
+        <v>3.171513938437671</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674761315132584</v>
+        <v>4.673858672159103</v>
       </c>
       <c r="K7" t="n">
-        <v>16.60179840254566</v>
+        <v>17.33001502292652</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23700766582924</v>
+        <v>42.19101919798801</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8931305712032</v>
+        <v>99.89441788553603</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.17031820479622</v>
+        <v>87.71941390282043</v>
       </c>
       <c r="C8" t="n">
-        <v>43.35517254642269</v>
+        <v>42.75304011994356</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004533878116865</v>
+        <v>1.973776163377921</v>
       </c>
       <c r="E8" t="n">
-        <v>9.686207867051088</v>
+        <v>9.581127533183842</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495342564831531</v>
+        <v>0.7494414791030997</v>
       </c>
       <c r="G8" t="n">
-        <v>31.00604246878198</v>
+        <v>30.541544953758</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47857579822504</v>
+        <v>34.47430803874258</v>
       </c>
       <c r="I8" t="n">
-        <v>5.560834833118391</v>
+        <v>5.715206490260596</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684589103019706</v>
+        <v>4.684009244394374</v>
       </c>
       <c r="K8" t="n">
-        <v>11.82968179520379</v>
+        <v>12.2805860971796</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63017336599078</v>
+        <v>44.77627974146954</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81502770761725</v>
+        <v>99.80990595859268</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.05797134558402</v>
+        <v>85.72359647050773</v>
       </c>
       <c r="C9" t="n">
-        <v>42.10630978248734</v>
+        <v>41.64385137631307</v>
       </c>
       <c r="D9" t="n">
-        <v>1.908789292182185</v>
+        <v>1.883686764565685</v>
       </c>
       <c r="E9" t="n">
-        <v>9.997282643974655</v>
+        <v>9.939065955240483</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508820336795269</v>
+        <v>0.7508319817027994</v>
       </c>
       <c r="G9" t="n">
-        <v>29.52506939566259</v>
+        <v>29.14753205871315</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54057354925823</v>
+        <v>34.53827115832877</v>
       </c>
       <c r="I9" t="n">
-        <v>4.642361720329792</v>
+        <v>4.771508666314353</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693012710497043</v>
+        <v>4.692699885642497</v>
       </c>
       <c r="K9" t="n">
-        <v>13.94202865441597</v>
+        <v>14.27640352949226</v>
       </c>
       <c r="L9" t="n">
-        <v>43.7971939288434</v>
+        <v>43.92098935835412</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84553236574672</v>
+        <v>99.84124426415944</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.74747067259331</v>
+        <v>83.60052359935069</v>
       </c>
       <c r="C10" t="n">
-        <v>40.51629515366514</v>
+        <v>40.26075342605316</v>
       </c>
       <c r="D10" t="n">
-        <v>1.805120897244643</v>
+        <v>1.788910625357172</v>
       </c>
       <c r="E10" t="n">
-        <v>10.10008630862491</v>
+        <v>10.10275196278998</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520400261410285</v>
+        <v>0.7520242556858616</v>
       </c>
       <c r="G10" t="n">
-        <v>27.9215311909985</v>
+        <v>27.68099812751674</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59384120248731</v>
+        <v>34.59311576154963</v>
       </c>
       <c r="I10" t="n">
-        <v>3.874600883715481</v>
+        <v>3.982571268414656</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700250163381428</v>
+        <v>4.700151598036636</v>
       </c>
       <c r="K10" t="n">
-        <v>16.25252932740671</v>
+        <v>16.39947640064932</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10222102669677</v>
+        <v>43.20722826589989</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87104550776861</v>
+        <v>99.86745809260238</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.29472442830031</v>
+        <v>81.2844448412838</v>
       </c>
       <c r="C11" t="n">
-        <v>38.66417119034324</v>
+        <v>38.5617411116738</v>
       </c>
       <c r="D11" t="n">
-        <v>1.696197407776926</v>
+        <v>1.686505927919237</v>
       </c>
       <c r="E11" t="n">
-        <v>10.02948555298849</v>
+        <v>10.07831708187826</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530369877105153</v>
+        <v>0.7530491449203818</v>
       </c>
       <c r="G11" t="n">
-        <v>26.2367074136839</v>
+        <v>26.09642246574357</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63970143468371</v>
+        <v>34.64026066633755</v>
       </c>
       <c r="I11" t="n">
-        <v>3.233114458266052</v>
+        <v>3.323332398732407</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706481173190721</v>
+        <v>4.706557155752387</v>
       </c>
       <c r="K11" t="n">
-        <v>18.70527557169969</v>
+        <v>18.7155551587162</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52292543563164</v>
+        <v>42.61207674993181</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89237219767458</v>
+        <v>99.88937302032181</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.82577464159917</v>
+        <v>79.01683731535061</v>
       </c>
       <c r="C12" t="n">
-        <v>36.69552125021787</v>
+        <v>36.80826103879667</v>
       </c>
       <c r="D12" t="n">
-        <v>1.587691180056606</v>
+        <v>1.587351234037478</v>
       </c>
       <c r="E12" t="n">
-        <v>9.837452394840151</v>
+        <v>9.947896707776783</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538959255346653</v>
+        <v>0.753929955732844</v>
       </c>
       <c r="G12" t="n">
-        <v>24.55833782285205</v>
+        <v>24.56213626006604</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67921257459461</v>
+        <v>34.68077796371082</v>
       </c>
       <c r="I12" t="n">
-        <v>2.697335209129415</v>
+        <v>2.772682970696374</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711849534591658</v>
+        <v>4.712062223330276</v>
       </c>
       <c r="K12" t="n">
-        <v>21.17422535840083</v>
+        <v>20.98316268464937</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04044465642947</v>
+        <v>42.11626148770028</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91019126504818</v>
+        <v>99.90768521114633</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.36085104449238</v>
+        <v>76.66767220835406</v>
       </c>
       <c r="C13" t="n">
-        <v>34.64708361633355</v>
+        <v>34.88724390765773</v>
       </c>
       <c r="D13" t="n">
-        <v>1.480384469139925</v>
+        <v>1.485541079248298</v>
       </c>
       <c r="E13" t="n">
-        <v>9.547569890904446</v>
+        <v>9.69533672027117</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546363817787936</v>
+        <v>0.7546881018936396</v>
       </c>
       <c r="G13" t="n">
-        <v>22.89852230554406</v>
+        <v>22.98676035020537</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71327356182451</v>
+        <v>34.71565268710741</v>
       </c>
       <c r="I13" t="n">
-        <v>2.249987049183192</v>
+        <v>2.31289263279292</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716477386117459</v>
+        <v>4.716800636835249</v>
       </c>
       <c r="K13" t="n">
-        <v>23.63914895550761</v>
+        <v>23.33232779164595</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63884145012744</v>
+        <v>41.70340932928807</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92507402196861</v>
+        <v>99.92298102859175</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.41419720482169</v>
+        <v>83.49597678858548</v>
       </c>
       <c r="C14" t="n">
-        <v>38.99200318368224</v>
+        <v>39.21677197800603</v>
       </c>
       <c r="D14" t="n">
-        <v>1.482153222584335</v>
+        <v>1.487228234891337</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9661544526775</v>
+        <v>12.09307908605743</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555380162713011</v>
+        <v>0.755545214704339</v>
       </c>
       <c r="G14" t="n">
-        <v>24.83474487628702</v>
+        <v>24.9254586335397</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66361231820372</v>
+        <v>36.66767168379611</v>
       </c>
       <c r="I14" t="n">
-        <v>2.989881717102203</v>
+        <v>2.844836343694444</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722112601695631</v>
+        <v>4.72215759190212</v>
       </c>
       <c r="K14" t="n">
-        <v>16.58580279517829</v>
+        <v>16.50402321141453</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32265023148893</v>
+        <v>44.1844845080025</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90045621034946</v>
+        <v>99.90527969742305</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.63943136906124</v>
+        <v>82.93013668176579</v>
       </c>
       <c r="C15" t="n">
-        <v>38.67908608165722</v>
+        <v>39.09058722121956</v>
       </c>
       <c r="D15" t="n">
-        <v>1.453618540809138</v>
+        <v>1.466771168419667</v>
       </c>
       <c r="E15" t="n">
-        <v>12.15145898928565</v>
+        <v>12.32222983451278</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562980925724487</v>
+        <v>0.7562658522688516</v>
       </c>
       <c r="G15" t="n">
-        <v>24.35662187846535</v>
+        <v>24.58260489250618</v>
       </c>
       <c r="H15" t="n">
-        <v>36.70049615758358</v>
+        <v>36.70264523813051</v>
       </c>
       <c r="I15" t="n">
-        <v>2.494074631767282</v>
+        <v>2.372958119247471</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726863078577804</v>
+        <v>4.726661576680324</v>
       </c>
       <c r="K15" t="n">
-        <v>17.36056863093875</v>
+        <v>17.06986331823423</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87729301748452</v>
+        <v>43.76052622877693</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91694773008049</v>
+        <v>99.92097676823072</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.21423965021442</v>
+        <v>80.62187111449478</v>
       </c>
       <c r="C16" t="n">
-        <v>36.63920503669789</v>
+        <v>37.14918369699861</v>
       </c>
       <c r="D16" t="n">
-        <v>1.361930071687704</v>
+        <v>1.379664720369644</v>
       </c>
       <c r="E16" t="n">
-        <v>11.73169203732482</v>
+        <v>11.92030257492041</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569518606847201</v>
+        <v>0.7568846723661627</v>
       </c>
       <c r="G16" t="n">
-        <v>22.82030316051406</v>
+        <v>23.12272932220136</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73222123309019</v>
+        <v>36.73267744761041</v>
       </c>
       <c r="I16" t="n">
-        <v>2.080192157633438</v>
+        <v>1.979083174738258</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7309491292795</v>
+        <v>4.730529202288518</v>
       </c>
       <c r="K16" t="n">
-        <v>19.78576034978556</v>
+        <v>19.37812888550524</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50575476263411</v>
+        <v>43.40677191418372</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93072014911758</v>
+        <v>99.93408449668757</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.02229494469466</v>
+        <v>82.49290552420243</v>
       </c>
       <c r="C17" t="n">
-        <v>37.94717946163732</v>
+        <v>38.51569267804456</v>
       </c>
       <c r="D17" t="n">
-        <v>1.363080995832203</v>
+        <v>1.380748830181606</v>
       </c>
       <c r="E17" t="n">
-        <v>12.55358270296215</v>
+        <v>12.76030264068165</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575915368258058</v>
+        <v>0.7574794154857928</v>
       </c>
       <c r="G17" t="n">
-        <v>23.30499219042001</v>
+        <v>23.64742656525267</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22866678613846</v>
+        <v>37.26806908480345</v>
       </c>
       <c r="I17" t="n">
-        <v>2.079433627354744</v>
+        <v>1.944632641011046</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734947105161286</v>
+        <v>4.734246346786206</v>
       </c>
       <c r="K17" t="n">
-        <v>17.97770505530534</v>
+        <v>17.50709447579759</v>
       </c>
       <c r="L17" t="n">
-        <v>44.00585955481262</v>
+        <v>43.91244265309942</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93074407175527</v>
+        <v>99.93522980694156</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.61336096783019</v>
+        <v>80.2749803806762</v>
       </c>
       <c r="C18" t="n">
-        <v>35.85912367519718</v>
+        <v>36.59812017488259</v>
       </c>
       <c r="D18" t="n">
-        <v>1.275789909596551</v>
+        <v>1.300583491144683</v>
       </c>
       <c r="E18" t="n">
-        <v>12.03867690271397</v>
+        <v>12.28971787149369</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581415928518951</v>
+        <v>0.7579894716913516</v>
       </c>
       <c r="G18" t="n">
-        <v>21.81255110347407</v>
+        <v>22.2744730442963</v>
       </c>
       <c r="H18" t="n">
-        <v>37.25569698844878</v>
+        <v>37.29316390522666</v>
       </c>
       <c r="I18" t="n">
-        <v>1.734119515420581</v>
+        <v>1.621618398752566</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738384955324344</v>
+        <v>4.737434198070948</v>
       </c>
       <c r="K18" t="n">
-        <v>20.38663903216982</v>
+        <v>19.72501961932381</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69647524742869</v>
+        <v>43.6228426324322</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9422379547957</v>
+        <v>99.94598242663858</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.68404840846719</v>
+        <v>79.41762992803449</v>
       </c>
       <c r="C19" t="n">
-        <v>35.19669688197079</v>
+        <v>35.99063820358885</v>
       </c>
       <c r="D19" t="n">
-        <v>1.242798731262321</v>
+        <v>1.270213386707321</v>
       </c>
       <c r="E19" t="n">
-        <v>11.96836125335681</v>
+        <v>12.22809157040623</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586060077100434</v>
+        <v>0.7584196403956902</v>
       </c>
       <c r="G19" t="n">
-        <v>21.24849133315751</v>
+        <v>21.75433875284294</v>
       </c>
       <c r="H19" t="n">
-        <v>37.27851871382994</v>
+        <v>37.31432825195829</v>
       </c>
       <c r="I19" t="n">
-        <v>1.445984820962803</v>
+        <v>1.352115573250941</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741287548187771</v>
+        <v>4.740122752473065</v>
       </c>
       <c r="K19" t="n">
-        <v>21.31595159153281</v>
+        <v>20.58237007196551</v>
       </c>
       <c r="L19" t="n">
-        <v>43.43918153995693</v>
+        <v>43.38194676892475</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95183001346054</v>
+        <v>99.95495504447912</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.15271994531426</v>
+        <v>77.01538165303593</v>
       </c>
       <c r="C20" t="n">
-        <v>32.88776008746748</v>
+        <v>33.79660890497181</v>
       </c>
       <c r="D20" t="n">
-        <v>1.152113206782741</v>
+        <v>1.184233775200994</v>
       </c>
       <c r="E20" t="n">
-        <v>11.29598157587638</v>
+        <v>11.58826841306963</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759006340550069</v>
+        <v>0.7587896860098317</v>
       </c>
       <c r="G20" t="n">
-        <v>19.6980145484009</v>
+        <v>20.28180696084613</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29819139650972</v>
+        <v>37.33253453615613</v>
       </c>
       <c r="I20" t="n">
-        <v>1.205623248756529</v>
+        <v>1.127312744191774</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743789628437931</v>
+        <v>4.742435537561449</v>
       </c>
       <c r="K20" t="n">
-        <v>23.84728005468574</v>
+        <v>22.98461834696407</v>
       </c>
       <c r="L20" t="n">
-        <v>43.22479361282004</v>
+        <v>43.18121398214047</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95983375497326</v>
+        <v>99.96244123407634</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.07681139471148</v>
+        <v>82.67876018209337</v>
       </c>
       <c r="C21" t="n">
-        <v>36.54811438811497</v>
+        <v>37.36893765979799</v>
       </c>
       <c r="D21" t="n">
-        <v>1.152933954779072</v>
+        <v>1.18496644253208</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2730013216934</v>
+        <v>13.50233749360218</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595470451696681</v>
+        <v>0.7592591375875068</v>
       </c>
       <c r="G21" t="n">
-        <v>21.38866838953302</v>
+        <v>21.94549417647641</v>
       </c>
       <c r="H21" t="n">
-        <v>39.00138333702139</v>
+        <v>39.0067707762504</v>
       </c>
       <c r="I21" t="n">
-        <v>1.754108314204511</v>
+        <v>1.534562545722882</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747169032310425</v>
+        <v>4.745369609921919</v>
       </c>
       <c r="K21" t="n">
-        <v>17.92318860528851</v>
+        <v>17.32123981790662</v>
       </c>
       <c r="L21" t="n">
-        <v>45.47026835314402</v>
+        <v>45.25870206488339</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94157134654751</v>
+        <v>99.948879542588</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_50_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.28058381978849</v>
+        <v>43.41732383053639</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1242315168494</v>
+        <v>97.00215576596111</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.97412231796558</v>
+        <v>81.60007039575473</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90425514520628</v>
+        <v>43.3556259513103</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228612641612747</v>
+        <v>2.186638997184483</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689483872280083</v>
+        <v>4.165325300307163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428708805375824</v>
+        <v>0.7377197883706209</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96520065574613</v>
+        <v>32.89069491598327</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17206050472879</v>
+        <v>33.93511026504856</v>
       </c>
       <c r="I3" t="n">
-        <v>6.532950759700363</v>
+        <v>3.073832451544253</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64294300335989</v>
+        <v>4.61074867731638</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02587768203442</v>
+        <v>18.39992960424526</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83535532847674</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7654881557174</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0282930925122</v>
+        <v>88.68381787453963</v>
       </c>
       <c r="C4" t="n">
-        <v>42.58769309690378</v>
+        <v>42.87238359158522</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182836651729841</v>
+        <v>2.192433154685252</v>
       </c>
       <c r="E4" t="n">
-        <v>6.481871377939024</v>
+        <v>6.501131867218382</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444231470448968</v>
+        <v>0.7396745987671963</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26755107207368</v>
+        <v>33.55274724209124</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24346476406525</v>
+        <v>34.02503154329103</v>
       </c>
       <c r="I4" t="n">
-        <v>5.455501410628896</v>
+        <v>7.049833226191558</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652644669030605</v>
+        <v>4.622966242294977</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97170690748779</v>
+        <v>11.31618212546037</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25912914117232</v>
+        <v>45.57706088487087</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8185291455639</v>
+        <v>99.76562660191645</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.73149626915436</v>
+        <v>87.78819906544868</v>
       </c>
       <c r="C5" t="n">
-        <v>42.13759395468361</v>
+        <v>43.06951155730883</v>
       </c>
       <c r="D5" t="n">
-        <v>2.119076002777747</v>
+        <v>2.150751398550521</v>
       </c>
       <c r="E5" t="n">
-        <v>7.051586194127362</v>
+        <v>7.358867227274394</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457413430424721</v>
+        <v>0.7413282760798962</v>
       </c>
       <c r="G5" t="n">
-        <v>32.29580605225215</v>
+        <v>32.91485439450023</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30410177995371</v>
+        <v>34.10110069967522</v>
       </c>
       <c r="I5" t="n">
-        <v>4.554301502985467</v>
+        <v>5.88799534386906</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660883394015451</v>
+        <v>4.633301725499351</v>
       </c>
       <c r="K5" t="n">
-        <v>14.26850373084564</v>
+        <v>12.21180093455133</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44236060861994</v>
+        <v>44.52285880741231</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84845829414918</v>
+        <v>99.80417129927247</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.28814907434025</v>
+        <v>86.6430755854301</v>
       </c>
       <c r="C6" t="n">
-        <v>41.40140427280026</v>
+        <v>42.83845494747941</v>
       </c>
       <c r="D6" t="n">
-        <v>2.048390542792962</v>
+        <v>2.096656050628161</v>
       </c>
       <c r="E6" t="n">
-        <v>7.449860977871965</v>
+        <v>7.993101962468395</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468623112740397</v>
+        <v>0.7427303220433671</v>
       </c>
       <c r="G6" t="n">
-        <v>31.21852335762939</v>
+        <v>32.0869853523207</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35566631860582</v>
+        <v>34.16559481399488</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80095612070332</v>
+        <v>4.915942571203542</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667889445462748</v>
+        <v>4.642064512771044</v>
       </c>
       <c r="K6" t="n">
-        <v>15.71185092565976</v>
+        <v>13.3569244145699</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76023642645705</v>
+        <v>43.64106521173213</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87349162491707</v>
+        <v>99.83644457378142</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.66998497707348</v>
+        <v>85.40566755774681</v>
       </c>
       <c r="C7" t="n">
-        <v>40.37338366462151</v>
+        <v>42.36483546133339</v>
       </c>
       <c r="D7" t="n">
-        <v>1.969498853817399</v>
+        <v>2.038402200148398</v>
       </c>
       <c r="E7" t="n">
-        <v>7.691522777279719</v>
+        <v>8.454883470963837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478173875454563</v>
+        <v>0.7439197652384386</v>
       </c>
       <c r="G7" t="n">
-        <v>30.01617352074315</v>
+        <v>31.19547506073024</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39959982709099</v>
+        <v>34.22030920096817</v>
       </c>
       <c r="I7" t="n">
-        <v>3.171513938437671</v>
+        <v>4.103179326957489</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673858672159103</v>
+        <v>4.649498532740241</v>
       </c>
       <c r="K7" t="n">
-        <v>17.33001502292652</v>
+        <v>14.59433244225318</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19101919798801</v>
+        <v>42.90427813610221</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89441788553603</v>
+        <v>99.86344603968877</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.71941390282043</v>
+        <v>83.88328617941393</v>
       </c>
       <c r="C8" t="n">
-        <v>42.75304011994356</v>
+        <v>41.480185136381</v>
       </c>
       <c r="D8" t="n">
-        <v>1.973776163377921</v>
+        <v>1.966636443957678</v>
       </c>
       <c r="E8" t="n">
-        <v>9.581127533183842</v>
+        <v>8.727874917983849</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494414791030997</v>
+        <v>0.7449319485252132</v>
       </c>
       <c r="G8" t="n">
-        <v>30.541544953758</v>
+        <v>30.09718010338617</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47430803874258</v>
+        <v>34.2668696321598</v>
       </c>
       <c r="I8" t="n">
-        <v>5.715206490260596</v>
+        <v>3.423968455118641</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684009244394374</v>
+        <v>4.655824678282582</v>
       </c>
       <c r="K8" t="n">
-        <v>12.2805860971796</v>
+        <v>16.11671382058608</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77627974146954</v>
+        <v>42.28912383950631</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80990595859268</v>
+        <v>99.88602279647338</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.72359647050773</v>
+        <v>82.37428162972822</v>
       </c>
       <c r="C9" t="n">
-        <v>41.64385137631307</v>
+        <v>40.50317003848922</v>
       </c>
       <c r="D9" t="n">
-        <v>1.883686764565685</v>
+        <v>1.89607400968439</v>
       </c>
       <c r="E9" t="n">
-        <v>9.939065955240483</v>
+        <v>8.890821787625635</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508319817027994</v>
+        <v>0.7457930492312742</v>
       </c>
       <c r="G9" t="n">
-        <v>29.14753205871315</v>
+        <v>29.01730064758666</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53827115832877</v>
+        <v>34.3064802646386</v>
       </c>
       <c r="I9" t="n">
-        <v>4.771508666314353</v>
+        <v>2.856605313266184</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692699885642497</v>
+        <v>4.661206557695463</v>
       </c>
       <c r="K9" t="n">
-        <v>14.27640352949226</v>
+        <v>17.6257183702718</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92098935835412</v>
+        <v>41.77600135637458</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84124426415944</v>
+        <v>99.90488976513559</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.60052359935069</v>
+        <v>86.6479366979321</v>
       </c>
       <c r="C10" t="n">
-        <v>40.26075342605316</v>
+        <v>43.45257600596793</v>
       </c>
       <c r="D10" t="n">
-        <v>1.788910625357172</v>
+        <v>1.898208134165727</v>
       </c>
       <c r="E10" t="n">
-        <v>10.10275196278998</v>
+        <v>10.59757188006161</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520242556858616</v>
+        <v>0.7466324759605293</v>
       </c>
       <c r="G10" t="n">
-        <v>27.68099812751674</v>
+        <v>30.25907152557179</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59311576154963</v>
+        <v>35.55420437422191</v>
       </c>
       <c r="I10" t="n">
-        <v>3.982571268414656</v>
+        <v>2.925795333197232</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700151598036636</v>
+        <v>4.666452974753308</v>
       </c>
       <c r="K10" t="n">
-        <v>16.39947640064932</v>
+        <v>13.3520633020679</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20722826589989</v>
+        <v>43.09794382832523</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86745809260238</v>
+        <v>99.90258313636106</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.2844448412838</v>
+        <v>86.61331045640333</v>
       </c>
       <c r="C11" t="n">
-        <v>38.5617411116738</v>
+        <v>43.80053509130641</v>
       </c>
       <c r="D11" t="n">
-        <v>1.686505927919237</v>
+        <v>1.893004030579899</v>
       </c>
       <c r="E11" t="n">
-        <v>10.07831708187826</v>
+        <v>11.00481271608409</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530491449203818</v>
+        <v>0.7473480625266227</v>
       </c>
       <c r="G11" t="n">
-        <v>26.09642246574357</v>
+        <v>30.1973495363114</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64026066633755</v>
+        <v>35.60951609170685</v>
       </c>
       <c r="I11" t="n">
-        <v>3.323332398732407</v>
+        <v>2.490354628403067</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706557155752387</v>
+        <v>4.670925390791392</v>
       </c>
       <c r="K11" t="n">
-        <v>18.7155551587162</v>
+        <v>13.38668954359668</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61207674993181</v>
+        <v>42.72984302805714</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88937302032181</v>
+        <v>99.91706766296022</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.01683731535061</v>
+        <v>85.01807842924973</v>
       </c>
       <c r="C12" t="n">
-        <v>36.80826103879667</v>
+        <v>42.59316490562662</v>
       </c>
       <c r="D12" t="n">
-        <v>1.587351234037478</v>
+        <v>1.824416125084426</v>
       </c>
       <c r="E12" t="n">
-        <v>9.947896707776783</v>
+        <v>10.9522472000281</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753929955732844</v>
+        <v>0.7479566511620178</v>
       </c>
       <c r="G12" t="n">
-        <v>24.56213626006604</v>
+        <v>29.1032298605198</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68077796371082</v>
+        <v>35.63851402171026</v>
       </c>
       <c r="I12" t="n">
-        <v>2.772682970696374</v>
+        <v>2.076985500982499</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712062223330276</v>
+        <v>4.674729069762611</v>
       </c>
       <c r="K12" t="n">
-        <v>20.98316268464937</v>
+        <v>14.98192157075028</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11626148770028</v>
+        <v>42.35573700616747</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90768521114633</v>
+        <v>99.93082348254435</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.66767220835406</v>
+        <v>86.19804099498396</v>
       </c>
       <c r="C13" t="n">
-        <v>34.88724390765773</v>
+        <v>43.58701135231279</v>
       </c>
       <c r="D13" t="n">
-        <v>1.485541079248298</v>
+        <v>1.825767407830682</v>
       </c>
       <c r="E13" t="n">
-        <v>9.69533672027117</v>
+        <v>11.59990498887429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546881018936396</v>
+        <v>0.7485106371215615</v>
       </c>
       <c r="G13" t="n">
-        <v>22.98676035020537</v>
+        <v>29.4451117299248</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71565268710741</v>
+        <v>35.9852363530074</v>
       </c>
       <c r="I13" t="n">
-        <v>2.31289263279292</v>
+        <v>1.915318396215462</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716800636835249</v>
+        <v>4.678191482009759</v>
       </c>
       <c r="K13" t="n">
-        <v>23.33232779164595</v>
+        <v>13.80195900501604</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70340932928807</v>
+        <v>42.54723294816455</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92298102859175</v>
+        <v>99.93620330549338</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.49597678858548</v>
+        <v>84.51152606628949</v>
       </c>
       <c r="C14" t="n">
-        <v>39.21677197800603</v>
+        <v>42.19879627897567</v>
       </c>
       <c r="D14" t="n">
-        <v>1.487228234891337</v>
+        <v>1.755047513552331</v>
       </c>
       <c r="E14" t="n">
-        <v>12.09307908605743</v>
+        <v>11.41677435015523</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755545214704339</v>
+        <v>0.7489821504819371</v>
       </c>
       <c r="G14" t="n">
-        <v>24.9254586335397</v>
+        <v>28.30457478111997</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66767168379611</v>
+        <v>36.00790472787775</v>
       </c>
       <c r="I14" t="n">
-        <v>2.844836343694444</v>
+        <v>1.597104102590168</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72215759190212</v>
+        <v>4.681138440512107</v>
       </c>
       <c r="K14" t="n">
-        <v>16.50402321141453</v>
+        <v>15.48847393371051</v>
       </c>
       <c r="L14" t="n">
-        <v>44.1844845080025</v>
+        <v>42.25952649853004</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90527969742305</v>
+        <v>99.94679671121622</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.93013668176579</v>
+        <v>83.79427101104383</v>
       </c>
       <c r="C15" t="n">
-        <v>39.09058722121956</v>
+        <v>41.71783771428828</v>
       </c>
       <c r="D15" t="n">
-        <v>1.466771168419667</v>
+        <v>1.725023772426449</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32222983451278</v>
+        <v>11.44535884125413</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562658522688516</v>
+        <v>0.7493823956205368</v>
       </c>
       <c r="G15" t="n">
-        <v>24.58260489250618</v>
+        <v>27.82036610907869</v>
       </c>
       <c r="H15" t="n">
-        <v>36.70264523813051</v>
+        <v>36.02714682705091</v>
       </c>
       <c r="I15" t="n">
-        <v>2.372958119247471</v>
+        <v>1.343353092984751</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726661576680324</v>
+        <v>4.683639972628355</v>
       </c>
       <c r="K15" t="n">
-        <v>17.06986331823423</v>
+        <v>16.20572898895619</v>
       </c>
       <c r="L15" t="n">
-        <v>43.76052622877693</v>
+        <v>42.03167877648568</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92097676823072</v>
+        <v>99.95524547973014</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.62187111449478</v>
+        <v>81.7445487016862</v>
       </c>
       <c r="C16" t="n">
-        <v>37.14918369699861</v>
+        <v>39.87698562749229</v>
       </c>
       <c r="D16" t="n">
-        <v>1.379664720369644</v>
+        <v>1.639513221011691</v>
       </c>
       <c r="E16" t="n">
-        <v>11.92030257492041</v>
+        <v>11.06466697974808</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568846723661627</v>
+        <v>0.7497246355360997</v>
       </c>
       <c r="G16" t="n">
-        <v>23.12272932220136</v>
+        <v>26.44129244958848</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73267744761041</v>
+        <v>36.04360027960079</v>
       </c>
       <c r="I16" t="n">
-        <v>1.979083174738258</v>
+        <v>1.119972164100439</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730529202288518</v>
+        <v>4.685778972100623</v>
       </c>
       <c r="K16" t="n">
-        <v>19.37812888550524</v>
+        <v>18.2554512983138</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40677191418372</v>
+        <v>41.83024771049989</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93408449668757</v>
+        <v>99.96268463630598</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.49290552420243</v>
+        <v>85.66427458566201</v>
       </c>
       <c r="C17" t="n">
-        <v>38.51569267804456</v>
+        <v>42.44537207046395</v>
       </c>
       <c r="D17" t="n">
-        <v>1.380748830181606</v>
+        <v>1.640329166211992</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76030264068165</v>
+        <v>12.45247804220888</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574794154857928</v>
+        <v>0.7500977549535421</v>
       </c>
       <c r="G17" t="n">
-        <v>23.64742656525267</v>
+        <v>27.62359111949275</v>
       </c>
       <c r="H17" t="n">
-        <v>37.26806908480345</v>
+        <v>37.23067778073698</v>
       </c>
       <c r="I17" t="n">
-        <v>1.944632641011046</v>
+        <v>1.278989753598231</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734246346786206</v>
+        <v>4.688110968459639</v>
       </c>
       <c r="K17" t="n">
-        <v>17.50709447579759</v>
+        <v>14.33572541433799</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91244265309942</v>
+        <v>43.17629073024342</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93522980694156</v>
+        <v>99.95738821504537</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.2749803806762</v>
+        <v>87.14935452039913</v>
       </c>
       <c r="C18" t="n">
-        <v>36.59812017488259</v>
+        <v>43.12024436966549</v>
       </c>
       <c r="D18" t="n">
-        <v>1.300583491144683</v>
+        <v>1.641611476463374</v>
       </c>
       <c r="E18" t="n">
-        <v>12.28971787149369</v>
+        <v>13.01193237036482</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579894716913516</v>
+        <v>0.7506841360656559</v>
       </c>
       <c r="G18" t="n">
-        <v>22.2744730442963</v>
+        <v>27.74972518896592</v>
       </c>
       <c r="H18" t="n">
-        <v>37.29316390522666</v>
+        <v>37.25978247555528</v>
       </c>
       <c r="I18" t="n">
-        <v>1.621618398752566</v>
+        <v>2.043843022573721</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737434198070948</v>
+        <v>4.691775850410349</v>
       </c>
       <c r="K18" t="n">
-        <v>19.72501961932381</v>
+        <v>12.85064547960088</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6228426324322</v>
+        <v>43.96103526681308</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94598242663858</v>
+        <v>99.93192511607946</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.41762992803449</v>
+        <v>84.863492435739</v>
       </c>
       <c r="C19" t="n">
-        <v>35.99063820358885</v>
+        <v>41.15195817366823</v>
       </c>
       <c r="D19" t="n">
-        <v>1.270213386707321</v>
+        <v>1.554155726971578</v>
       </c>
       <c r="E19" t="n">
-        <v>12.22809157040623</v>
+        <v>12.60278752728933</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584196403956902</v>
+        <v>0.7511866776591274</v>
       </c>
       <c r="G19" t="n">
-        <v>21.75433875284294</v>
+        <v>26.27137720627469</v>
       </c>
       <c r="H19" t="n">
-        <v>37.31432825195829</v>
+        <v>37.28472584328888</v>
       </c>
       <c r="I19" t="n">
-        <v>1.352115573250941</v>
+        <v>1.704342718885855</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740122752473065</v>
+        <v>4.694916735369546</v>
       </c>
       <c r="K19" t="n">
-        <v>20.58237007196551</v>
+        <v>15.13650756426098</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38194676892475</v>
+        <v>43.65476084477707</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95495504447912</v>
+        <v>99.94322658270629</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.01538165303593</v>
+        <v>82.47024678718839</v>
       </c>
       <c r="C20" t="n">
-        <v>33.79660890497181</v>
+        <v>39.02297575615603</v>
       </c>
       <c r="D20" t="n">
-        <v>1.184233775200994</v>
+        <v>1.46299381799111</v>
       </c>
       <c r="E20" t="n">
-        <v>11.58826841306963</v>
+        <v>12.10039770218138</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587896860098317</v>
+        <v>0.751618151424134</v>
       </c>
       <c r="G20" t="n">
-        <v>20.28180696084613</v>
+        <v>24.73038047338182</v>
       </c>
       <c r="H20" t="n">
-        <v>37.33253453615613</v>
+        <v>37.30614179955554</v>
       </c>
       <c r="I20" t="n">
-        <v>1.127312744191774</v>
+        <v>1.42110139625358</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742435537561449</v>
+        <v>4.697613446400837</v>
       </c>
       <c r="K20" t="n">
-        <v>22.98461834696407</v>
+        <v>17.5297532128116</v>
       </c>
       <c r="L20" t="n">
-        <v>43.18121398214047</v>
+        <v>43.39992817772998</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96244123407634</v>
+        <v>99.9526571466976</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.67876018209337</v>
+        <v>79.97687269028164</v>
       </c>
       <c r="C21" t="n">
-        <v>37.36893765979799</v>
+        <v>36.7493912419958</v>
       </c>
       <c r="D21" t="n">
-        <v>1.18496644253208</v>
+        <v>1.368411167298361</v>
       </c>
       <c r="E21" t="n">
-        <v>13.50233749360218</v>
+        <v>11.51557882327672</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592591375875068</v>
+        <v>0.7519893188195025</v>
       </c>
       <c r="G21" t="n">
-        <v>21.94549417647641</v>
+        <v>23.13155967930321</v>
       </c>
       <c r="H21" t="n">
-        <v>39.0067707762504</v>
+        <v>37.32456448327699</v>
       </c>
       <c r="I21" t="n">
-        <v>1.534562545722882</v>
+        <v>1.184835975684966</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745369609921919</v>
+        <v>4.699933242621889</v>
       </c>
       <c r="K21" t="n">
-        <v>17.32123981790662</v>
+        <v>20.02312730971835</v>
       </c>
       <c r="L21" t="n">
-        <v>45.25870206488339</v>
+        <v>43.18800640950103</v>
       </c>
       <c r="M21" t="n">
-        <v>99.948879542588</v>
+        <v>99.96052496121519</v>
       </c>
     </row>
   </sheetData>
